--- a/diseases/d239/2020-2025.xlsx
+++ b/diseases/d239/2020-2025.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23660,7 +23660,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24441,7 +24441,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26003,7 +26003,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26784,7 +26784,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27565,7 +27565,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30689,7 +30689,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31470,7 +31470,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33032,7 +33032,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35375,7 +35375,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36937,7 +36937,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37718,7 +37718,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39280,7 +39280,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40061,7 +40061,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -40842,7 +40842,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42404,7 +42404,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43185,7 +43185,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43966,7 +43966,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44747,7 +44747,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45528,7 +45528,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46309,7 +46309,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47090,7 +47090,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -47871,7 +47871,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48652,7 +48652,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49433,7 +49433,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -50214,7 +50214,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -50995,7 +50995,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52557,7 +52557,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53338,7 +53338,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54119,7 +54119,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -54900,7 +54900,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -55681,7 +55681,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -56462,7 +56462,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN287" t="b">

--- a/diseases/d239/2020-2025.xlsx
+++ b/diseases/d239/2020-2025.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23660,7 +23660,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24441,7 +24441,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26003,7 +26003,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26784,7 +26784,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27565,7 +27565,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30689,7 +30689,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31470,7 +31470,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33032,7 +33032,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35375,7 +35375,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36937,7 +36937,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37718,7 +37718,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39280,7 +39280,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40061,7 +40061,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -40842,7 +40842,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42404,7 +42404,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43185,7 +43185,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43966,7 +43966,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44747,7 +44747,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45528,7 +45528,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46309,7 +46309,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47090,7 +47090,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -47871,7 +47871,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48652,7 +48652,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49433,7 +49433,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -50214,7 +50214,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -50995,7 +50995,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52557,7 +52557,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53338,7 +53338,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54119,7 +54119,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -54900,7 +54900,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -55681,7 +55681,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -56462,7 +56462,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN287" t="b">
